--- a/business_surveys/028_series_creation_survey--business_surveys.xlsx
+++ b/business_surveys/028_series_creation_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'young_adults'}</t>
+          <t>young_adults</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Young Adults'}</t>
+          <t>Young Adults</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'adults'}</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Adults'}</t>
+          <t>Adults</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'old_adults'}</t>
+          <t>old_adults</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Old Adults'}</t>
+          <t>Old Adults</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'in_development'}</t>
+          <t>in_development</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'In Development'}</t>
+          <t>In Development</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'development'}</t>
+          <t>development</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Development'}</t>
+          <t>Development</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'production'}</t>
+          <t>production</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Production'}</t>
+          <t>Production</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'design'}</t>
+          <t>design</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Design'}</t>
+          <t>Design</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'research'}</t>
+          <t>research</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Research'}</t>
+          <t>Research</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'in_development'}</t>
+          <t>in_development</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'In Development'}</t>
+          <t>In Development</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'chat_jimmy'}</t>
+          <t>chat_jimmy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Chat Jimmy'}</t>
+          <t>Chat Jimmy</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'series'}</t>
+          <t>series</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Series'}</t>
+          <t>Series</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'show'}</t>
+          <t>show</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Show'}</t>
+          <t>Show</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'product'}</t>
+          <t>product</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Product'}</t>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'book'}</t>
+          <t>book</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Book'}</t>
+          <t>Book</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'movie'}</t>
+          <t>movie</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Movie'}</t>
+          <t>Movie</t>
         </is>
       </c>
     </row>
